--- a/Design/Datas/条件表.xlsx
+++ b/Design/Datas/条件表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re764451737aa48df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb682a2eb36434a50"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -320,10 +320,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="1" t="str">
-        <x:v>始终成立</x:v>
+        <x:v>测试剧情尚未完成</x:v>
       </x:c>
       <x:c r="D5" s="1" t="str">
-        <x:v>{始终成立}</x:v>
+        <x:v>{游戏布尔变量,1,false}</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
